--- a/etf_holdings/2026-08-27_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:05</t>
+          <t>2026-08-27 16:55:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:06</t>
+          <t>2026-08-27 16:55:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:07</t>
+          <t>2026-08-27 16:55:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:09</t>
+          <t>2026-08-27 16:55:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:09</t>
+          <t>2026-08-27 16:55:44</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:09</t>
+          <t>2026-08-27 16:55:44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:09</t>
+          <t>2026-08-27 16:55:44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:09</t>
+          <t>2026-08-27 16:55:44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-27_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.80%4,200,000</t>
+          <t>11.74%4,200,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.80%</t>
+          <t>11.74%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.60%1,400,000</t>
+          <t>8.93%1,400,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.60%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.70%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2059川湖科技</t>
+          <t>2408南亞科技</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0%14340</t>
+          <t>+4.64%541</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+4.64%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14340</v>
+        <v>541</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.61%510,000</t>
+          <t>8.78%14,000,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.61%</t>
+          <t>8.78%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>510000</v>
+        <v>14000000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2408南亞科技</t>
+          <t>2059川湖科技</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+4.64%541</t>
+          <t>0%14340</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+4.64%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>541</v>
+        <v>14340</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.42%14,000,000</t>
+          <t>8.48%510,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.42%</t>
+          <t>8.48%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14000000</v>
+        <v>510000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.75%5,000,000</t>
+          <t>6.84%5,000,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.75%</t>
+          <t>6.84%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.81%7,700,000</t>
+          <t>4.96%7,700,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.81%</t>
+          <t>4.96%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6669緯穎科技</t>
+          <t>8046南亞電路</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.44%6815</t>
+          <t>+9.75%1295</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>+9.75%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1295</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4.88%3,250,000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>+0.44%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>6815</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4.74%600,000</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>4.74%</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>600000</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2454聯發科技</t>
+          <t>3017奇鋐科技</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.03%3865</t>
+          <t>+5.86%3340</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>+5.86%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3865</v>
+        <v>3340</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.59%1,000,000</t>
+          <t>4.84%1,250,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.84%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1000000</v>
+        <v>1250000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3017奇鋐科技</t>
+          <t>6669緯穎科技</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+5.86%3340</t>
+          <t>+0.44%6815</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3340</v>
+        <v>6815</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.59%1,250,000</t>
+          <t>4.74%600,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.74%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1250000</v>
+        <v>600000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8046南亞電路</t>
+          <t>2454聯發科技</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+9.75%1295</t>
+          <t>-2.03%3865</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+9.75%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1295</v>
+        <v>3865</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.46%3,250,000</t>
+          <t>4.48%1,000,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>4.48%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>3250000</v>
+        <v>1000000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6274台燿科技</t>
+          <t>3189景碩科技</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-5.56%1445</t>
+          <t>+3.75%914</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+3.75%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1445</v>
+        <v>914</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.27%2,400,000</t>
+          <t>4.34%4,100,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2400000</v>
+        <v>4100000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3189景碩科技</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+3.75%914</t>
+          <t>+1.7%2090</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+3.75%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>914</v>
+        <v>2090</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.20%4,100,000</t>
+          <t>4.12%1,700,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4100000</v>
+        <v>1700000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>6274台燿科技</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+1.7%2090</t>
+          <t>-5.56%1445</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2090</v>
+        <v>1445</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.07%1,700,000</t>
+          <t>4.02%2,400,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>4.02%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1700000</v>
+        <v>2400000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6223旺矽科技</t>
+          <t>3081聯亞光電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.99%5090</t>
+          <t>+3.53%3370</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+3.53%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5090</v>
+        <v>3370</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.28%560,000</t>
+          <t>3.13%800,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>560000</v>
+        <v>800000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:40</t>
+          <t>2026-08-27 17:13:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>6223旺矽科技</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.16%6345</t>
+          <t>+0.99%5090</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6345</v>
+        <v>5090</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.65%360,000</t>
+          <t>2.71%460,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>360000</v>
+        <v>460000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,25 +1419,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3081聯亞光電</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+3.53%3370</t>
+          <t>+0.16%6345</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3370</v>
+        <v>6345</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.65%700,000</t>
+          <t>2.65%360,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1446,11 +1446,11 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>700000</v>
+        <v>360000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.27%340,000</t>
+          <t>2.23%340,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,25 +1541,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.45%15305</t>
+          <t>+1.41%2155</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>15305</v>
+        <v>2155</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.20%120,500</t>
+          <t>2.20%880,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1568,11 +1568,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>120500</v>
+        <v>880000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.41%2155</t>
+          <t>-2.45%15305</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2155</v>
+        <v>15305</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.18%880,000</t>
+          <t>2.14%120,500</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>880000</v>
+        <v>120500</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.93%2,700,000</t>
+          <t>2.11%2,700,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:41</t>
+          <t>2026-08-27 17:13:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:42</t>
+          <t>2026-08-27 17:13:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:44</t>
+          <t>2026-08-27 17:13:33</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:44</t>
+          <t>2026-08-27 17:13:33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:44</t>
+          <t>2026-08-27 17:13:33</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:44</t>
+          <t>2026-08-27 17:13:33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:44</t>
+          <t>2026-08-27 17:13:33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-27_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:29</t>
+          <t>2026-08-27 19:37:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:30</t>
+          <t>2026-08-27 19:37:25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:32</t>
+          <t>2026-08-27 19:37:27</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:33</t>
+          <t>2026-08-27 19:37:28</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:33</t>
+          <t>2026-08-27 19:37:28</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:33</t>
+          <t>2026-08-27 19:37:28</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:33</t>
+          <t>2026-08-27 19:37:28</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:33</t>
+          <t>2026-08-27 19:37:28</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-27_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:24</t>
+          <t>2026-08-27 22:47:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:25</t>
+          <t>2026-08-27 22:47:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:27</t>
+          <t>2026-08-27 22:47:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:28</t>
+          <t>2026-08-27 22:47:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:28</t>
+          <t>2026-08-27 22:47:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:28</t>
+          <t>2026-08-27 22:47:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:28</t>
+          <t>2026-08-27 22:47:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:28</t>
+          <t>2026-08-27 22:47:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
